--- a/docs/project-management/03_Design/lld/lld-master-register.xlsx
+++ b/docs/project-management/03_Design/lld/lld-master-register.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d752cb73b61fc091/Desktop/linuxlabs/projectredstone/docs/project-management/03_Design/lld/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="14_{D44A9173-D2B5-4790-8BE7-D58BC91E8DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A56884B2-2BD2-455A-8C08-97F233266982}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="14_{D44A9173-D2B5-4790-8BE7-D58BC91E8DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBD1DADD-A5D5-4614-A75E-3C2DB084EC8F}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="11" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2985" yWindow="2985" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -911,41 +911,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF44546A"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE7EDF4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -956,6 +922,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2679,6 +2649,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8837DA2-F01F-4122-BD59-31B64678213D}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="21.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="45" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
